--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2639,6 +2639,237 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125792725</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fula kärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>566396</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6516647</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125830049</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105348</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dalstugevägen 15 V 135 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>566514</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6516694</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström, Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,6 +2870,325 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125909164</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>566259</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6516831</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spår på flera träd.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125909132</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>566356</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6516828</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125909112</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fula kärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>566537</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6516672</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flera träd med spår av hack/födosök.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105348</v>
+        <v>105355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91244</v>
+        <v>91247</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2644,7 +2644,7 @@
         <v>125792725</v>
       </c>
       <c r="B20" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125909164</v>
       </c>
       <c r="B22" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>125909112</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3189,6 +3189,235 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126234735</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57812</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>566232</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6516593</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosök i tallar.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126227339</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57474</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>566456</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6516756</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2644,7 +2644,7 @@
         <v>125792725</v>
       </c>
       <c r="B20" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125909164</v>
       </c>
       <c r="B22" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>125909112</v>
       </c>
       <c r="B24" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>126234735</v>
       </c>
       <c r="B25" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>126227339</v>
       </c>
       <c r="B26" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -2644,7 +2644,7 @@
         <v>125792725</v>
       </c>
       <c r="B20" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>125830049</v>
       </c>
       <c r="B21" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125909164</v>
       </c>
       <c r="B22" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>125909132</v>
       </c>
       <c r="B23" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>125909112</v>
       </c>
       <c r="B24" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>126234735</v>
       </c>
       <c r="B25" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>126227339</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3418,6 +3418,322 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127781243</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90095</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1593</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lakritsmusseron</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tricholoma apium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>566469</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6516700</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Några meter från fyndplatsen för blå taggsvamp.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127781279</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92650</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>566520</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6516651</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127781295</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91964</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Simonstorp längs stigen, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>566278</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6516601</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90095</v>
+        <v>90101</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91964</v>
+        <v>91970</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90101</v>
+        <v>90104</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90104</v>
+        <v>90112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91973</v>
+        <v>91981</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90112</v>
+        <v>90113</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,6 +3733,212 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128165522</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>566384</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6516802</v>
+      </c>
+      <c r="S30" t="n">
+        <v>100</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128165225</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92668</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>566364</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6516867</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90113</v>
+        <v>90114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91982</v>
+        <v>91983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128165225</v>
       </c>
       <c r="B31" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90114</v>
+        <v>90115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91983</v>
+        <v>91984</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128165225</v>
       </c>
       <c r="B31" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3940,6 +3940,1267 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128311598</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>566335</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6516702</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128311589</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92670</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>566440</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6516738</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128311599</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>566338</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6516704</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128311596</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>566398</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6516610</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128311604</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>566323</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6516629</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128311595</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>566399</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6516608</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128311597</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>566348</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6516642</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128311593</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>566425</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6516705</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128311594</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>566402</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6516622</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128311592</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>566429</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6516716</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128311603</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>566294</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6516657</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128311588</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>566365</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6516666</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128311591</v>
+      </c>
+      <c r="B44" t="n">
+        <v>96758</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>566434</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6516780</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5201,6 +5201,111 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128381935</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90121</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1593</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lakritsmusseron</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tricholoma apium</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>566299</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6516658</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90115</v>
+        <v>90121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91984</v>
+        <v>91992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>128165522</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128165225</v>
       </c>
       <c r="B31" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>128311598</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>128311589</v>
       </c>
       <c r="B33" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>128311599</v>
       </c>
       <c r="B34" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128311596</v>
       </c>
       <c r="B35" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>128311604</v>
       </c>
       <c r="B36" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>128311595</v>
       </c>
       <c r="B37" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128311597</v>
       </c>
       <c r="B38" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>128311593</v>
       </c>
       <c r="B39" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128311594</v>
       </c>
       <c r="B40" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>128311592</v>
       </c>
       <c r="B41" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>128311603</v>
       </c>
       <c r="B42" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>128311588</v>
       </c>
       <c r="B43" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>128311591</v>
       </c>
       <c r="B44" t="n">
-        <v>96758</v>
+        <v>96766</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3423,7 +3423,7 @@
         <v>127781243</v>
       </c>
       <c r="B27" t="n">
-        <v>90121</v>
+        <v>90213</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127781279</v>
       </c>
       <c r="B28" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127781295</v>
       </c>
       <c r="B29" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>128165522</v>
       </c>
       <c r="B30" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128165225</v>
       </c>
       <c r="B31" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>128311598</v>
       </c>
       <c r="B32" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>128311589</v>
       </c>
       <c r="B33" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>128311599</v>
       </c>
       <c r="B34" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128311596</v>
       </c>
       <c r="B35" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>128311604</v>
       </c>
       <c r="B36" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>128311595</v>
       </c>
       <c r="B37" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128311597</v>
       </c>
       <c r="B38" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>128311593</v>
       </c>
       <c r="B39" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128311594</v>
       </c>
       <c r="B40" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>128311592</v>
       </c>
       <c r="B41" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>128311603</v>
       </c>
       <c r="B42" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128311588</v>
+        <v>128311591</v>
       </c>
       <c r="B43" t="n">
-        <v>92650</v>
+        <v>96859</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566365</v>
+        <v>566434</v>
       </c>
       <c r="R43" t="n">
-        <v>6516666</v>
+        <v>6516780</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128311591</v>
+        <v>128311588</v>
       </c>
       <c r="B44" t="n">
-        <v>96766</v>
+        <v>92742</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566434</v>
+        <v>566365</v>
       </c>
       <c r="R44" t="n">
-        <v>6516780</v>
+        <v>6516666</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5206,7 +5206,7 @@
         <v>128381935</v>
       </c>
       <c r="B45" t="n">
-        <v>90121</v>
+        <v>90213</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -4815,32 +4815,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128311592</v>
+        <v>128311603</v>
       </c>
       <c r="B41" t="n">
-        <v>92742</v>
+        <v>92734</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566429</v>
+        <v>566294</v>
       </c>
       <c r="R41" t="n">
-        <v>6516716</v>
+        <v>6516657</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4912,32 +4912,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128311603</v>
+        <v>128311592</v>
       </c>
       <c r="B42" t="n">
-        <v>92734</v>
+        <v>92742</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566294</v>
+        <v>566429</v>
       </c>
       <c r="R42" t="n">
-        <v>6516657</v>
+        <v>6516716</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128311591</v>
+        <v>128311588</v>
       </c>
       <c r="B43" t="n">
-        <v>96859</v>
+        <v>92742</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566434</v>
+        <v>566365</v>
       </c>
       <c r="R43" t="n">
-        <v>6516780</v>
+        <v>6516666</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128311588</v>
+        <v>128311591</v>
       </c>
       <c r="B44" t="n">
-        <v>92742</v>
+        <v>96859</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566365</v>
+        <v>566434</v>
       </c>
       <c r="R44" t="n">
-        <v>6516666</v>
+        <v>6516780</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128311588</v>
+        <v>128311591</v>
       </c>
       <c r="B43" t="n">
-        <v>92742</v>
+        <v>96859</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566365</v>
+        <v>566434</v>
       </c>
       <c r="R43" t="n">
-        <v>6516666</v>
+        <v>6516780</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128311591</v>
+        <v>128311588</v>
       </c>
       <c r="B44" t="n">
-        <v>96859</v>
+        <v>92742</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566434</v>
+        <v>566365</v>
       </c>
       <c r="R44" t="n">
-        <v>6516780</v>
+        <v>6516666</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3739,7 +3739,7 @@
         <v>128165522</v>
       </c>
       <c r="B30" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128165225</v>
       </c>
       <c r="B31" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>128311598</v>
       </c>
       <c r="B32" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>128311589</v>
       </c>
       <c r="B33" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>128311599</v>
       </c>
       <c r="B34" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128311596</v>
       </c>
       <c r="B35" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>128311604</v>
       </c>
       <c r="B36" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>128311595</v>
       </c>
       <c r="B37" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128311597</v>
       </c>
       <c r="B38" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>128311593</v>
       </c>
       <c r="B39" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128311594</v>
       </c>
       <c r="B40" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,32 +4815,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128311603</v>
+        <v>128311592</v>
       </c>
       <c r="B41" t="n">
-        <v>92734</v>
+        <v>92754</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566294</v>
+        <v>566429</v>
       </c>
       <c r="R41" t="n">
-        <v>6516657</v>
+        <v>6516716</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4912,32 +4912,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128311592</v>
+        <v>128311603</v>
       </c>
       <c r="B42" t="n">
-        <v>92742</v>
+        <v>92746</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566429</v>
+        <v>566294</v>
       </c>
       <c r="R42" t="n">
-        <v>6516716</v>
+        <v>6516657</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128311591</v>
+        <v>128311588</v>
       </c>
       <c r="B43" t="n">
-        <v>96859</v>
+        <v>92754</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566434</v>
+        <v>566365</v>
       </c>
       <c r="R43" t="n">
-        <v>6516780</v>
+        <v>6516666</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128311588</v>
+        <v>128311591</v>
       </c>
       <c r="B44" t="n">
-        <v>92742</v>
+        <v>96871</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566365</v>
+        <v>566434</v>
       </c>
       <c r="R44" t="n">
-        <v>6516666</v>
+        <v>6516780</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5206,7 +5206,7 @@
         <v>128381935</v>
       </c>
       <c r="B45" t="n">
-        <v>90213</v>
+        <v>90225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5306,6 +5306,107 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128718611</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>566388</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6516673</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3844,7 +3844,7 @@
         <v>128165225</v>
       </c>
       <c r="B31" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>128311598</v>
       </c>
       <c r="B32" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>128311589</v>
       </c>
       <c r="B33" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>128311599</v>
       </c>
       <c r="B34" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128311596</v>
       </c>
       <c r="B35" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>128311604</v>
       </c>
       <c r="B36" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>128311595</v>
       </c>
       <c r="B37" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128311597</v>
       </c>
       <c r="B38" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>128311593</v>
       </c>
       <c r="B39" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128311594</v>
       </c>
       <c r="B40" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>128311592</v>
       </c>
       <c r="B41" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>128311603</v>
       </c>
       <c r="B42" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>128311588</v>
       </c>
       <c r="B43" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>128311591</v>
       </c>
       <c r="B44" t="n">
-        <v>96871</v>
+        <v>96873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>128381935</v>
       </c>
       <c r="B45" t="n">
-        <v>90225</v>
+        <v>90227</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5407,6 +5407,1576 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128775265</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>566384</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6516767</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128775249</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>566253</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6516592</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128775261</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>566377</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6516675</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128775264</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>566399</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6516690</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128775263</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>566387</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6516687</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128775274</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>566125</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6516587</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128775268</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>566333</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6516703</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128775250</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>566250</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6516594</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128775272</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>566307</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6516659</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128775266</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>566363</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6516787</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128775270</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>566353</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6516641</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128775259</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>566376</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6516661</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128775258</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>566408</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6516617</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128775267</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>566359</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6516764</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128775269</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>566332</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6516705</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128775271</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>566325</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6516646</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3844,7 +3844,7 @@
         <v>128165225</v>
       </c>
       <c r="B31" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>128311598</v>
       </c>
       <c r="B32" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>128311589</v>
       </c>
       <c r="B33" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>128311599</v>
       </c>
       <c r="B34" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128311596</v>
       </c>
       <c r="B35" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>128311595</v>
       </c>
       <c r="B37" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128311597</v>
       </c>
       <c r="B38" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>128311593</v>
       </c>
       <c r="B39" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128311594</v>
       </c>
       <c r="B40" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>128311592</v>
       </c>
       <c r="B41" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>128311603</v>
       </c>
       <c r="B42" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>128311588</v>
       </c>
       <c r="B43" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>128311591</v>
       </c>
       <c r="B44" t="n">
-        <v>96873</v>
+        <v>96874</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5806,32 +5806,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92792</v>
+        <v>92757</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R51" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5903,32 +5903,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92756</v>
+        <v>92793</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R52" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6003,7 +6003,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6203,32 +6203,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92792</v>
+        <v>92757</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R55" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6300,32 +6300,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92756</v>
+        <v>92793</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R56" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6400,7 +6400,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6688,32 +6688,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92792</v>
+        <v>92757</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R60" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6785,32 +6785,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92756</v>
+        <v>92793</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R61" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6885,7 +6885,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5311,7 +5311,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5806,32 +5806,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B51" t="n">
-        <v>92757</v>
+        <v>92820</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R51" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5903,32 +5903,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B52" t="n">
-        <v>92793</v>
+        <v>92784</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R52" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6003,7 +6003,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6203,32 +6203,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B55" t="n">
-        <v>92757</v>
+        <v>92820</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R55" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6300,32 +6300,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B56" t="n">
-        <v>92793</v>
+        <v>92784</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R56" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6400,7 +6400,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6688,32 +6688,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B60" t="n">
-        <v>92757</v>
+        <v>92820</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R60" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6785,32 +6785,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B61" t="n">
-        <v>92793</v>
+        <v>92784</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R61" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6885,7 +6885,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3945,7 +3945,7 @@
         <v>128311598</v>
       </c>
       <c r="B32" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>128311589</v>
       </c>
       <c r="B33" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>128311599</v>
       </c>
       <c r="B34" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128311596</v>
       </c>
       <c r="B35" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>128311604</v>
       </c>
       <c r="B36" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>128311595</v>
       </c>
       <c r="B37" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128311597</v>
       </c>
       <c r="B38" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>128311593</v>
       </c>
       <c r="B39" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128311594</v>
       </c>
       <c r="B40" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,32 +4815,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128311592</v>
+        <v>128311603</v>
       </c>
       <c r="B41" t="n">
-        <v>92757</v>
+        <v>92776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566429</v>
+        <v>566294</v>
       </c>
       <c r="R41" t="n">
-        <v>6516716</v>
+        <v>6516657</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4912,32 +4912,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128311603</v>
+        <v>128311592</v>
       </c>
       <c r="B42" t="n">
-        <v>92749</v>
+        <v>92784</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566294</v>
+        <v>566429</v>
       </c>
       <c r="R42" t="n">
-        <v>6516657</v>
+        <v>6516716</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128311588</v>
+        <v>128311591</v>
       </c>
       <c r="B43" t="n">
-        <v>92757</v>
+        <v>96901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566365</v>
+        <v>566434</v>
       </c>
       <c r="R43" t="n">
-        <v>6516666</v>
+        <v>6516780</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128311591</v>
+        <v>128311588</v>
       </c>
       <c r="B44" t="n">
-        <v>96874</v>
+        <v>92784</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566434</v>
+        <v>566365</v>
       </c>
       <c r="R44" t="n">
-        <v>6516780</v>
+        <v>6516666</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5206,7 +5206,7 @@
         <v>128381935</v>
       </c>
       <c r="B45" t="n">
-        <v>90227</v>
+        <v>90254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5806,32 +5806,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92820</v>
+        <v>92784</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R51" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5903,32 +5903,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92784</v>
+        <v>92820</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R52" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6203,32 +6203,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92820</v>
+        <v>92784</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R55" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6300,32 +6300,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92784</v>
+        <v>92820</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R56" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6688,32 +6688,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92820</v>
+        <v>92784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R60" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6785,32 +6785,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92784</v>
+        <v>92820</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R61" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5311,7 +5311,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6688,32 +6688,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B60" t="n">
-        <v>92784</v>
+        <v>92825</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R60" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6785,32 +6785,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B61" t="n">
-        <v>92820</v>
+        <v>92789</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R61" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6885,7 +6885,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -3945,7 +3945,7 @@
         <v>128311598</v>
       </c>
       <c r="B32" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>128311589</v>
       </c>
       <c r="B33" t="n">
-        <v>92812</v>
+        <v>92823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,21 +4052,12 @@
       <c r="E33" t="n">
         <v>5449</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4139,7 +4130,7 @@
         <v>128311599</v>
       </c>
       <c r="B34" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,7 +4227,7 @@
         <v>128311596</v>
       </c>
       <c r="B35" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4324,7 @@
         <v>128311604</v>
       </c>
       <c r="B36" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4421,7 @@
         <v>128311595</v>
       </c>
       <c r="B37" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,7 +4518,7 @@
         <v>128311597</v>
       </c>
       <c r="B38" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4624,7 +4615,7 @@
         <v>128311593</v>
       </c>
       <c r="B39" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4712,7 @@
         <v>128311594</v>
       </c>
       <c r="B40" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,32 +4806,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128311603</v>
+        <v>128311592</v>
       </c>
       <c r="B41" t="n">
-        <v>92776</v>
+        <v>92794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4850,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566294</v>
+        <v>566429</v>
       </c>
       <c r="R41" t="n">
-        <v>6516657</v>
+        <v>6516716</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4912,32 +4903,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128311592</v>
+        <v>128311603</v>
       </c>
       <c r="B42" t="n">
-        <v>92784</v>
+        <v>92786</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4947,10 +4938,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566429</v>
+        <v>566294</v>
       </c>
       <c r="R42" t="n">
-        <v>6516716</v>
+        <v>6516657</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5012,7 +5003,7 @@
         <v>128311591</v>
       </c>
       <c r="B43" t="n">
-        <v>96901</v>
+        <v>96914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5109,7 +5100,7 @@
         <v>128311588</v>
       </c>
       <c r="B44" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,7 +5197,7 @@
         <v>128381935</v>
       </c>
       <c r="B45" t="n">
-        <v>90254</v>
+        <v>90264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5311,7 +5302,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5409,45 +5400,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128775265</v>
+        <v>128775249</v>
       </c>
       <c r="B47" t="n">
-        <v>92789</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566384</v>
+        <v>566253</v>
       </c>
       <c r="R47" t="n">
-        <v>6516767</v>
+        <v>6516592</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5488,6 +5487,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5499,60 +5499,52 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128775249</v>
+        <v>128775265</v>
       </c>
       <c r="B48" t="n">
-        <v>98625</v>
+        <v>92794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566253</v>
+        <v>566384</v>
       </c>
       <c r="R48" t="n">
-        <v>6516592</v>
+        <v>6516767</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5593,7 +5585,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5605,7 +5596,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5615,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5712,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5806,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B51" t="n">
-        <v>92789</v>
+        <v>92832</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5841,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R51" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5903,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B52" t="n">
-        <v>92825</v>
+        <v>92794</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5938,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R52" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6003,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6100,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6206,7 +6197,7 @@
         <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6303,7 +6294,7 @@
         <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6400,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6497,7 +6488,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6594,7 +6585,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6691,7 +6682,7 @@
         <v>128775267</v>
       </c>
       <c r="B60" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6788,7 +6779,7 @@
         <v>128775269</v>
       </c>
       <c r="B61" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6885,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6895,21 +6886,12 @@
       <c r="E62" t="n">
         <v>5449</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6679,32 +6679,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92832</v>
+        <v>92794</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R60" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92794</v>
+        <v>92832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R61" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6959,6 +6959,665 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128926697</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>566368</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6516759</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spår efter födosök på trädstam.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128926722</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>566385</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6516690</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spår efter födosök på trädstam.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128926499</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>566216</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6516615</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spår efter födosök på trädstam.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128926621</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>566310</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6516696</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spår av födosök på trädstam.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128926592</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>566238</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6516650</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128926673</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>566315</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6516759</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spår av födosök på sex träd nära varandra i ett blötare parti av skogen.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B58" t="n">
-        <v>92794</v>
+        <v>92786</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R58" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B59" t="n">
-        <v>92786</v>
+        <v>92794</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R59" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5000,10 +5000,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128311591</v>
+        <v>128311588</v>
       </c>
       <c r="B43" t="n">
-        <v>96914</v>
+        <v>92794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566434</v>
+        <v>566365</v>
       </c>
       <c r="R43" t="n">
-        <v>6516780</v>
+        <v>6516666</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5097,10 +5097,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128311588</v>
+        <v>128311591</v>
       </c>
       <c r="B44" t="n">
-        <v>92794</v>
+        <v>96914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566365</v>
+        <v>566434</v>
       </c>
       <c r="R44" t="n">
-        <v>6516666</v>
+        <v>6516780</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5302,7 +5302,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,53 +5400,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128775249</v>
+        <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>92798</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566253</v>
+        <v>566384</v>
       </c>
       <c r="R47" t="n">
-        <v>6516592</v>
+        <v>6516767</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5487,7 +5479,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5499,52 +5490,60 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128775265</v>
+        <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>92794</v>
+        <v>98636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566384</v>
+        <v>566253</v>
       </c>
       <c r="R48" t="n">
-        <v>6516767</v>
+        <v>6516592</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5585,6 +5584,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5797,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92832</v>
+        <v>92798</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R51" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5894,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92794</v>
+        <v>92836</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R52" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92786</v>
+        <v>92798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R58" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92794</v>
+        <v>92790</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R59" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6679,32 +6679,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B60" t="n">
-        <v>92794</v>
+        <v>92836</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R60" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B61" t="n">
-        <v>92832</v>
+        <v>92798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R61" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128926697</v>
       </c>
       <c r="B63" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>128926722</v>
       </c>
       <c r="B64" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>128926499</v>
       </c>
       <c r="B65" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>128926621</v>
       </c>
       <c r="B66" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>128926673</v>
       </c>
       <c r="B68" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5197,7 +5197,7 @@
         <v>128381935</v>
       </c>
       <c r="B45" t="n">
-        <v>90264</v>
+        <v>90268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B58" t="n">
-        <v>92798</v>
+        <v>92790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R58" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B59" t="n">
-        <v>92790</v>
+        <v>92798</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R59" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92790</v>
+        <v>92798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R58" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92798</v>
+        <v>92790</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R59" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6679,32 +6679,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92836</v>
+        <v>92798</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R60" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92798</v>
+        <v>92836</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R61" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5197,7 +5197,7 @@
         <v>128381935</v>
       </c>
       <c r="B45" t="n">
-        <v>90268</v>
+        <v>90273</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B58" t="n">
-        <v>92798</v>
+        <v>92795</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R58" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B59" t="n">
-        <v>92790</v>
+        <v>92803</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R59" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6682,7 +6682,7 @@
         <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128926697</v>
       </c>
       <c r="B63" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>128926722</v>
       </c>
       <c r="B64" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>128926499</v>
       </c>
       <c r="B65" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>128926621</v>
       </c>
       <c r="B66" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>128926673</v>
       </c>
       <c r="B68" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5797,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92849</v>
+        <v>92811</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R51" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5894,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92811</v>
+        <v>92849</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R52" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5302,7 +5302,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5302,7 +5302,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6194,32 +6194,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B55" t="n">
-        <v>92816</v>
+        <v>92857</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R55" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6291,32 +6291,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B56" t="n">
-        <v>92854</v>
+        <v>92819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R56" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5400,45 +5400,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128775265</v>
+        <v>128775249</v>
       </c>
       <c r="B47" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566384</v>
+        <v>566253</v>
       </c>
       <c r="R47" t="n">
-        <v>6516767</v>
+        <v>6516592</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5479,6 +5487,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5490,60 +5499,52 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128775249</v>
+        <v>128775265</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566253</v>
+        <v>566384</v>
       </c>
       <c r="R48" t="n">
-        <v>6516592</v>
+        <v>6516767</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5584,7 +5585,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5400,53 +5400,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128775249</v>
+        <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566253</v>
+        <v>566384</v>
       </c>
       <c r="R47" t="n">
-        <v>6516592</v>
+        <v>6516767</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5487,7 +5479,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5499,52 +5490,60 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128775265</v>
+        <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566384</v>
+        <v>566253</v>
       </c>
       <c r="R48" t="n">
-        <v>6516767</v>
+        <v>6516592</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5585,6 +5584,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>92811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R58" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B59" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R59" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5302,7 +5302,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,45 +5400,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128775265</v>
+        <v>128775249</v>
       </c>
       <c r="B47" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566384</v>
+        <v>566253</v>
       </c>
       <c r="R47" t="n">
-        <v>6516767</v>
+        <v>6516592</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5479,6 +5487,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5490,60 +5499,52 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128775249</v>
+        <v>128775265</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566253</v>
+        <v>566384</v>
       </c>
       <c r="R48" t="n">
-        <v>6516592</v>
+        <v>6516767</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5584,7 +5585,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6194,32 +6194,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92857</v>
+        <v>92826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R55" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6291,32 +6291,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92819</v>
+        <v>92864</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R56" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92811</v>
+        <v>92826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R58" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92819</v>
+        <v>92818</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R59" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6679,32 +6679,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B60" t="n">
-        <v>92819</v>
+        <v>92864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R60" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B61" t="n">
-        <v>92857</v>
+        <v>92826</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R61" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128926697</v>
       </c>
       <c r="B63" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>128926722</v>
       </c>
       <c r="B64" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>128926499</v>
       </c>
       <c r="B65" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>128926621</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>128926673</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5797,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B51" t="n">
-        <v>92826</v>
+        <v>92864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R51" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5894,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B52" t="n">
-        <v>92864</v>
+        <v>92826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R52" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6679,32 +6679,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92864</v>
+        <v>92826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R60" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92826</v>
+        <v>92864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R61" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5400,53 +5400,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128775249</v>
+        <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566253</v>
+        <v>566384</v>
       </c>
       <c r="R47" t="n">
-        <v>6516592</v>
+        <v>6516767</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5487,7 +5479,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5499,52 +5490,60 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128775265</v>
+        <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566384</v>
+        <v>566253</v>
       </c>
       <c r="R48" t="n">
-        <v>6516767</v>
+        <v>6516592</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5585,6 +5584,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5797,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92864</v>
+        <v>92833</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R51" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5894,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92826</v>
+        <v>92871</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R52" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6187,39 +6187,39 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B55" t="n">
-        <v>92826</v>
+        <v>92871</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R55" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6291,32 +6291,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B56" t="n">
-        <v>92864</v>
+        <v>92833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R56" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5302,7 +5302,7 @@
         <v>128718611</v>
       </c>
       <c r="B46" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5797,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B51" t="n">
-        <v>92833</v>
+        <v>92873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R51" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5894,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B52" t="n">
-        <v>92871</v>
+        <v>92835</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R52" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6187,39 +6187,39 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B55" t="n">
-        <v>92871</v>
+        <v>92835</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R55" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6291,32 +6291,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B56" t="n">
-        <v>92833</v>
+        <v>92873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R56" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B58" t="n">
-        <v>92833</v>
+        <v>92827</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R58" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B59" t="n">
-        <v>92825</v>
+        <v>92835</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R59" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6682,7 +6682,7 @@
         <v>128775269</v>
       </c>
       <c r="B60" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128775267</v>
       </c>
       <c r="B61" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128926697</v>
       </c>
       <c r="B63" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>128926722</v>
       </c>
       <c r="B64" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>128926499</v>
       </c>
       <c r="B65" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>128926621</v>
       </c>
       <c r="B66" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>128926673</v>
       </c>
       <c r="B68" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -6485,32 +6485,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128775258</v>
+        <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92827</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566408</v>
+        <v>566376</v>
       </c>
       <c r="R58" t="n">
-        <v>6516617</v>
+        <v>6516661</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6582,32 +6582,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128775259</v>
+        <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92835</v>
+        <v>92827</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566376</v>
+        <v>566408</v>
       </c>
       <c r="R59" t="n">
-        <v>6516661</v>
+        <v>6516617</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5797,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B51" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R51" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5894,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B52" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R52" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -5403,7 +5403,7 @@
         <v>128775265</v>
       </c>
       <c r="B47" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>128775249</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>128775261</v>
       </c>
       <c r="B49" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>128775264</v>
       </c>
       <c r="B50" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5797,32 +5797,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128775274</v>
+        <v>128775263</v>
       </c>
       <c r="B51" t="n">
-        <v>92835</v>
+        <v>92859</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566125</v>
+        <v>566387</v>
       </c>
       <c r="R51" t="n">
-        <v>6516587</v>
+        <v>6516687</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5894,32 +5894,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128775263</v>
+        <v>128775274</v>
       </c>
       <c r="B52" t="n">
-        <v>92873</v>
+        <v>92821</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566387</v>
+        <v>566125</v>
       </c>
       <c r="R52" t="n">
-        <v>6516687</v>
+        <v>6516587</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5994,7 +5994,7 @@
         <v>128775268</v>
       </c>
       <c r="B53" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>128775250</v>
       </c>
       <c r="B54" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6194,32 +6194,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128775266</v>
+        <v>128775272</v>
       </c>
       <c r="B55" t="n">
-        <v>92835</v>
+        <v>92859</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566363</v>
+        <v>566307</v>
       </c>
       <c r="R55" t="n">
-        <v>6516787</v>
+        <v>6516659</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6291,32 +6291,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128775272</v>
+        <v>128775266</v>
       </c>
       <c r="B56" t="n">
-        <v>92873</v>
+        <v>92821</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566307</v>
+        <v>566363</v>
       </c>
       <c r="R56" t="n">
-        <v>6516659</v>
+        <v>6516787</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>128775270</v>
       </c>
       <c r="B57" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>128775259</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>128775258</v>
       </c>
       <c r="B59" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6679,32 +6679,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128775269</v>
+        <v>128775267</v>
       </c>
       <c r="B60" t="n">
-        <v>92835</v>
+        <v>92859</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566332</v>
+        <v>566359</v>
       </c>
       <c r="R60" t="n">
-        <v>6516705</v>
+        <v>6516764</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128775267</v>
+        <v>128775269</v>
       </c>
       <c r="B61" t="n">
-        <v>92873</v>
+        <v>92821</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566359</v>
+        <v>566332</v>
       </c>
       <c r="R61" t="n">
-        <v>6516764</v>
+        <v>6516705</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6876,7 +6876,7 @@
         <v>128775271</v>
       </c>
       <c r="B62" t="n">
-        <v>92864</v>
+        <v>92850</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7404,7 +7404,7 @@
         <v>128926592</v>
       </c>
       <c r="B67" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7618,6 +7618,977 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131737805</v>
+      </c>
+      <c r="B69" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stora Skogsgården Väst, Ög</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>566497</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6516650</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131732756</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stora Skogsgården Väst, Ög</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>566589</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6516629</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131740388</v>
+      </c>
+      <c r="B71" t="n">
+        <v>93145</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stora Skogsgården Väst, Ög</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>566479</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6516672</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131740387</v>
+      </c>
+      <c r="B72" t="n">
+        <v>93145</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Simonstorp Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>566420</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6516809</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131737806</v>
+      </c>
+      <c r="B73" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stora Skogsgården Väst, Ög</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>566473</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6516637</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131740082</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91849</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Simonstorp Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>566369</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6516842</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131737269</v>
+      </c>
+      <c r="B75" t="n">
+        <v>93108</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fula kärret Väst, Ög</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>566086</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6516585</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131737270</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93108</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fula kärret Väst, Ög</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>566077</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6516582</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131737813</v>
+      </c>
+      <c r="B77" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Simonstorp Öst, Ög</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>566402</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6516844</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7623,7 +7623,7 @@
         <v>131737805</v>
       </c>
       <c r="B69" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>131732756</v>
       </c>
       <c r="B70" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>131740388</v>
       </c>
       <c r="B71" t="n">
-        <v>93145</v>
+        <v>93146</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>131740387</v>
       </c>
       <c r="B72" t="n">
-        <v>93145</v>
+        <v>93146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>131737806</v>
       </c>
       <c r="B73" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>131740082</v>
       </c>
       <c r="B74" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>131737269</v>
       </c>
       <c r="B75" t="n">
-        <v>93108</v>
+        <v>93109</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>131737270</v>
       </c>
       <c r="B76" t="n">
-        <v>93108</v>
+        <v>93109</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>131737813</v>
       </c>
       <c r="B77" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7623,7 +7623,7 @@
         <v>131737805</v>
       </c>
       <c r="B69" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>131732756</v>
       </c>
       <c r="B70" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>131740388</v>
       </c>
       <c r="B71" t="n">
-        <v>93146</v>
+        <v>93149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>131740387</v>
       </c>
       <c r="B72" t="n">
-        <v>93146</v>
+        <v>93149</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>131737806</v>
       </c>
       <c r="B73" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>131740082</v>
       </c>
       <c r="B74" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>131737269</v>
       </c>
       <c r="B75" t="n">
-        <v>93109</v>
+        <v>93112</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>131737270</v>
       </c>
       <c r="B76" t="n">
-        <v>93109</v>
+        <v>93112</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>131737813</v>
       </c>
       <c r="B77" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7943,10 +7943,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740387</v>
+        <v>131737806</v>
       </c>
       <c r="B72" t="n">
-        <v>93149</v>
+        <v>93158</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7954,34 +7954,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Simonstorp Öst, Ög</t>
+          <t>Stora Skogsgården Väst, Ög</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566420</v>
+        <v>566473</v>
       </c>
       <c r="R72" t="n">
-        <v>6516809</v>
+        <v>6516637</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8018,7 +8022,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8027,7 +8031,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8050,10 +8053,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737806</v>
+        <v>131740387</v>
       </c>
       <c r="B73" t="n">
-        <v>93158</v>
+        <v>93149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8061,38 +8064,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stora Skogsgården Väst, Ög</t>
+          <t>Simonstorp Öst, Ög</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566473</v>
+        <v>566420</v>
       </c>
       <c r="R73" t="n">
-        <v>6516637</v>
+        <v>6516809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8129,7 +8128,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8138,6 +8137,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7623,7 +7623,7 @@
         <v>131737805</v>
       </c>
       <c r="B69" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>131732756</v>
       </c>
       <c r="B70" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>131740388</v>
       </c>
       <c r="B71" t="n">
-        <v>93149</v>
+        <v>93155</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,10 +7943,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737806</v>
+        <v>131740387</v>
       </c>
       <c r="B72" t="n">
-        <v>93158</v>
+        <v>93155</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7954,38 +7954,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stora Skogsgården Väst, Ög</t>
+          <t>Simonstorp Öst, Ög</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566473</v>
+        <v>566420</v>
       </c>
       <c r="R72" t="n">
-        <v>6516637</v>
+        <v>6516809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8022,7 +8018,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8031,6 +8027,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8053,10 +8050,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131740387</v>
+        <v>131737806</v>
       </c>
       <c r="B73" t="n">
-        <v>93149</v>
+        <v>93164</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8064,34 +8061,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Simonstorp Öst, Ög</t>
+          <t>Stora Skogsgården Väst, Ög</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566420</v>
+        <v>566473</v>
       </c>
       <c r="R73" t="n">
-        <v>6516809</v>
+        <v>6516637</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8128,7 +8129,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8137,7 +8138,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>131740082</v>
       </c>
       <c r="B74" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>131737269</v>
       </c>
       <c r="B75" t="n">
-        <v>93112</v>
+        <v>93118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>131737270</v>
       </c>
       <c r="B76" t="n">
-        <v>93112</v>
+        <v>93118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>131737813</v>
       </c>
       <c r="B77" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7943,10 +7943,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740387</v>
+        <v>131737806</v>
       </c>
       <c r="B72" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7954,34 +7954,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Simonstorp Öst, Ög</t>
+          <t>Stora Skogsgården Väst, Ög</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566420</v>
+        <v>566473</v>
       </c>
       <c r="R72" t="n">
-        <v>6516809</v>
+        <v>6516637</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8018,7 +8022,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8027,7 +8031,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8050,10 +8053,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737806</v>
+        <v>131740387</v>
       </c>
       <c r="B73" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8061,38 +8064,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stora Skogsgården Väst, Ög</t>
+          <t>Simonstorp Öst, Ög</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566473</v>
+        <v>566420</v>
       </c>
       <c r="R73" t="n">
-        <v>6516637</v>
+        <v>6516809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8129,7 +8128,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8138,6 +8137,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7943,10 +7943,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737806</v>
+        <v>131740387</v>
       </c>
       <c r="B72" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7954,38 +7954,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stora Skogsgården Väst, Ög</t>
+          <t>Simonstorp Öst, Ög</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566473</v>
+        <v>566420</v>
       </c>
       <c r="R72" t="n">
-        <v>6516637</v>
+        <v>6516809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8022,7 +8018,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8031,6 +8027,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8053,10 +8050,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131740387</v>
+        <v>131737806</v>
       </c>
       <c r="B73" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8064,34 +8061,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Simonstorp Öst, Ög</t>
+          <t>Stora Skogsgården Väst, Ög</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566420</v>
+        <v>566473</v>
       </c>
       <c r="R73" t="n">
-        <v>6516809</v>
+        <v>6516637</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8128,7 +8129,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8137,7 +8138,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7623,7 +7623,7 @@
         <v>131737805</v>
       </c>
       <c r="B69" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>131732756</v>
       </c>
       <c r="B70" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>131740388</v>
       </c>
       <c r="B71" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>131740387</v>
       </c>
       <c r="B72" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>131737806</v>
       </c>
       <c r="B73" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>131740082</v>
       </c>
       <c r="B74" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>131737269</v>
       </c>
       <c r="B75" t="n">
-        <v>93118</v>
+        <v>93121</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>131737270</v>
       </c>
       <c r="B76" t="n">
-        <v>93118</v>
+        <v>93121</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>131737813</v>
       </c>
       <c r="B77" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7623,7 +7623,7 @@
         <v>131737805</v>
       </c>
       <c r="B69" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>131732756</v>
       </c>
       <c r="B70" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>131740388</v>
       </c>
       <c r="B71" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>131740387</v>
       </c>
       <c r="B72" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>131737806</v>
       </c>
       <c r="B73" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>131740082</v>
       </c>
       <c r="B74" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>131737269</v>
       </c>
       <c r="B75" t="n">
-        <v>93121</v>
+        <v>93126</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>131737270</v>
       </c>
       <c r="B76" t="n">
-        <v>93121</v>
+        <v>93126</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>131737813</v>
       </c>
       <c r="B77" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -7623,7 +7623,7 @@
         <v>131737805</v>
       </c>
       <c r="B69" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>131732756</v>
       </c>
       <c r="B70" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>131740388</v>
       </c>
       <c r="B71" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>131740387</v>
       </c>
       <c r="B72" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>131737806</v>
       </c>
       <c r="B73" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>131740082</v>
       </c>
       <c r="B74" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>131737269</v>
       </c>
       <c r="B75" t="n">
-        <v>93169</v>
+        <v>93172</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>131737270</v>
       </c>
       <c r="B76" t="n">
-        <v>93169</v>
+        <v>93172</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>131737813</v>
       </c>
       <c r="B77" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2025 artfynd.xlsx
+++ b/artfynd/A 24615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118706197</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035721</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035722</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180599</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127781243</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128381935</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485886</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736580</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311591</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734522</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118906278</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2011,6 +2076,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111684639</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186107</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186156</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311594</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311595</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311596</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311597</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311598</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311603</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775258</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2997,6 +3112,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775268</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3094,6 +3214,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775270</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3204,6 +3329,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737267</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3314,6 +3444,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737268</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3424,6 +3559,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737269</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3534,6 +3674,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737270</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3639,6 +3784,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111684610</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3748,6 +3898,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119179681</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3853,6 +4008,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186096</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3950,6 +4110,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311605</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4051,6 +4216,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186299</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4160,6 +4330,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180136</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4269,6 +4444,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180314</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4370,6 +4550,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119759946</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4467,6 +4652,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311588</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4564,6 +4754,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311592</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4661,6 +4856,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311593</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4758,6 +4958,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311599</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4855,6 +5060,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311606</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4952,6 +5162,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775259</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5049,6 +5264,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775264</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5146,6 +5366,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775265</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5243,6 +5468,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775266</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5340,6 +5570,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775269</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5437,6 +5672,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775274</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5534,6 +5774,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775277</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5643,6 +5888,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128926592</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5749,6 +5999,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732756</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5855,6 +6110,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732757</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5956,6 +6216,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732771</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6063,6 +6328,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118701733</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6168,6 +6438,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125909132</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6269,6 +6544,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740082</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6374,6 +6654,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111717434</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6480,6 +6765,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740339</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6587,6 +6877,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740371</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6694,6 +6989,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740372</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6801,6 +7101,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740387</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6908,6 +7213,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740388</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7015,6 +7325,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740389</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7122,6 +7437,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740403</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7227,6 +7547,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112273632</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7328,6 +7653,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120325960</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7429,6 +7759,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128718587</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7530,6 +7865,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128718611</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7627,6 +7967,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775261</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7724,6 +8069,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775263</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7821,6 +8171,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775267</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7918,6 +8273,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775272</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8015,6 +8375,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775275</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8125,6 +8490,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737796</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8235,6 +8605,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737804</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8345,6 +8720,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737805</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8455,6 +8835,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737806</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8565,6 +8950,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737811</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8675,6 +9065,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737812</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8783,6 +9178,11 @@
       <c r="AY80" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737813</t>
         </is>
       </c>
     </row>
@@ -8886,6 +9286,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186092</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8991,6 +9396,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127781295</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9092,6 +9502,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733372</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9193,6 +9608,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734667</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9294,6 +9714,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734668</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9391,6 +9816,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311604</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9503,6 +9933,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125792725</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9610,6 +10045,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125909112</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9717,6 +10157,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125909164</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9822,6 +10267,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165522</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9932,6 +10382,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128926499</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10042,6 +10497,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128926621</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10152,6 +10612,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128926673</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10262,6 +10727,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128926697</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10372,6 +10842,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128926722</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10477,6 +10952,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126227339</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10601,6 +11081,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234735</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10707,6 +11192,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775249</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10813,6 +11303,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775250</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10919,6 +11414,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775252</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11025,6 +11525,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775253</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11131,6 +11636,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775369</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11250,6 +11760,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830049</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11351,8 +11866,118 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186128</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>